--- a/Reports/Holden_Eagle_Midterm_WorkLog.xlsx
+++ b/Reports/Holden_Eagle_Midterm_WorkLog.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mohid\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mohid\OneDrive\Documents\GitHub\Concept-Mapping-Concept-Extraction\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE087FD7-ACDB-4F5A-83EA-D54E89BF0993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B24D2E-E03C-4718-A3D4-72F450DD6940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9525" yWindow="0" windowWidth="9750" windowHeight="11355" xr2:uid="{A8750DDA-DDDA-4226-B514-AF8B4DDDAD05}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{A8750DDA-DDDA-4226-B514-AF8B4DDDAD05}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>Date</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t>Modified Training set for new Model</t>
+  </si>
+  <si>
+    <t>Total Time Spent (hours)</t>
   </si>
 </sst>
 </file>
@@ -485,6 +488,7 @@
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="28.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.2265625" customWidth="1"/>
+    <col min="5" max="5" width="19.953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.75">
@@ -497,6 +501,9 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A2" s="2">
@@ -508,6 +515,10 @@
       <c r="C2" s="1">
         <v>1</v>
       </c>
+      <c r="E2">
+        <f>SUM(C2:C20)</f>
+        <v>52.5</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A3" s="2">
@@ -518,10 +529,6 @@
       </c>
       <c r="C3" s="1">
         <v>5</v>
-      </c>
-      <c r="E3">
-        <f>SUM(C2:C20)</f>
-        <v>52.5</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.75">
